--- a/data/demo/documents/D-20_office_supplies.xlsx
+++ b/data/demo/documents/D-20_office_supplies.xlsx
@@ -426,14 +426,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>date,description,qty_kg,amount_cny</t>
+          <t>date,description,qty_kg,amount_usd</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-27,A4 copy paper and toner cartridges,780,9400</t>
+          <t>2026-06-27,A4 copy paper and toner cartridges,780,1310</t>
         </is>
       </c>
     </row>
